--- a/Employee_Reports_wi48/Jimmy Mallari Dela Cruz Q0482.xlsx
+++ b/Employee_Reports_wi48/Jimmy Mallari Dela Cruz Q0482.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-48</v>
+        <v>-51</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-279</v>
+        <v>-282</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-341</v>
+        <v>-344</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1157,53 +1157,53 @@
       <c r="K15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>14-Jul-2025</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>14-Jul-2026</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-95</v>
+        <v>-98</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1263,9 +1263,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>10-Apr-2025</t>
@@ -1277,11 +1289,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-94</v>
+        <v>-97</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1314,11 +1326,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1351,11 +1363,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1388,11 +1400,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1437,11 +1449,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1474,11 +1486,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1719,7 +1731,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>7639</v>
+        <v>7636</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -1748,7 +1760,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7838</v>
+        <v>7835</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
